--- a/database/flash_1.xlsx
+++ b/database/flash_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\kawkab\backend\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76ECE761-2B39-4B38-9052-B7F47C5081A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46043357-BF5B-4A85-9FF7-FC548F090C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3132" yWindow="2124" windowWidth="13200" windowHeight="9840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="97">
   <si>
     <t>متى انتهت الحرب العالمية الثانية؟</t>
   </si>
@@ -311,144 +311,6 @@
   </si>
   <si>
     <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd3</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd4</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd5</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd6</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd7</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd8</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd9</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd10</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd11</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd12</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd13</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd14</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd15</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd16</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd17</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd18</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd19</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd20</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd21</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd22</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd23</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd24</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd25</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd26</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd27</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd28</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd29</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd30</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd31</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd32</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd33</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd34</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd35</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd36</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd37</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd38</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd39</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd40</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd41</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd42</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd43</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd44</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd45</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd46</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd47</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd48</t>
-  </si>
-  <si>
-    <t>fa51fb7f-6470-47ae-a998-d8b4317d7bd49</t>
   </si>
 </sst>
 </file>
@@ -784,7 +646,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -795,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -806,7 +668,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -817,7 +679,7 @@
         <v>9</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -828,7 +690,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -839,7 +701,7 @@
         <v>13</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -850,7 +712,7 @@
         <v>15</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -861,7 +723,7 @@
         <v>17</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -872,7 +734,7 @@
         <v>19</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -883,7 +745,7 @@
         <v>21</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -894,7 +756,7 @@
         <v>23</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -905,7 +767,7 @@
         <v>25</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -916,7 +778,7 @@
         <v>27</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -927,7 +789,7 @@
         <v>29</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -938,7 +800,7 @@
         <v>31</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -949,7 +811,7 @@
         <v>33</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -960,7 +822,7 @@
         <v>35</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -971,7 +833,7 @@
         <v>37</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -982,7 +844,7 @@
         <v>39</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -993,7 +855,7 @@
         <v>41</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1004,7 +866,7 @@
         <v>43</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1015,7 +877,7 @@
         <v>45</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1026,7 +888,7 @@
         <v>47</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1037,7 +899,7 @@
         <v>49</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1048,7 +910,7 @@
         <v>51</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1059,7 +921,7 @@
         <v>53</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1070,7 +932,7 @@
         <v>55</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1081,7 +943,7 @@
         <v>57</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1092,7 +954,7 @@
         <v>59</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1103,7 +965,7 @@
         <v>61</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1114,7 +976,7 @@
         <v>63</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1125,7 +987,7 @@
         <v>65</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1136,7 +998,7 @@
         <v>67</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1147,7 +1009,7 @@
         <v>69</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1158,7 +1020,7 @@
         <v>71</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1169,7 +1031,7 @@
         <v>73</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>132</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1180,7 +1042,7 @@
         <v>75</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1191,7 +1053,7 @@
         <v>77</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>134</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1202,7 +1064,7 @@
         <v>79</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>135</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1213,7 +1075,7 @@
         <v>81</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>136</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1224,7 +1086,7 @@
         <v>83</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>137</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1235,7 +1097,7 @@
         <v>85</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>138</v>
+        <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1246,7 +1108,7 @@
         <v>87</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1257,7 +1119,7 @@
         <v>89</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>140</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1268,7 +1130,7 @@
         <v>91</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1279,7 +1141,7 @@
         <v>9</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>142</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
